--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-03-2026.xlsx
@@ -1754,7 +1754,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£39.99</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£40.48</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>£744.00</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>£28.56</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>£34.78</t>
+          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>£38.19</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>£44.55</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>£47.47</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>£51.26</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>£46.92</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>£1201.6</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>£1337.92</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>£1276.0</t>
+          <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
